--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487424_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487424_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. MUJICA LANDAETA</t>
+          <t>M. CACHOPAS GIL PRATES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9636</v>
+        <v>5.3852</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4541</v>
+        <v>3.0245</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5095</v>
+        <v>2.3607</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8787</v>
+        <v>1.3816</v>
       </c>
       <c r="H2" t="n">
-        <v>1.964</v>
+        <v>1.5688</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9147</v>
+        <v>-0.1872</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5443</v>
+        <v>2.4514</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7765</v>
+        <v>2.5177</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7679</v>
+        <v>-0.0664</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6656</v>
+        <v>-1.0698</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8124</v>
+        <v>-0.9489</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1468</v>
+        <v>-0.1209</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3709</v>
+        <v>1.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3958</v>
+        <v>-0.3307</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1317</v>
+        <v>-0.6434</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5275</v>
+        <v>0.3127</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2767</v>
+        <v>3.1592</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X2" t="n">
-        <v>1.2767</v>
+        <v>1.9426</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. CACHOPAS GIL PRATES</t>
+          <t>S. MUJICA LANDAETA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7188</v>
+        <v>4.021</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5987</v>
+        <v>1.2065</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1201</v>
+        <v>2.8145</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3816</v>
+        <v>2.8787</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5688</v>
+        <v>1.964</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1872</v>
+        <v>0.9147</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4514</v>
+        <v>3.5443</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5177</v>
+        <v>2.7765</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0664</v>
+        <v>0.7679</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0698</v>
+        <v>-0.6656</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9489</v>
+        <v>-0.8124</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1209</v>
+        <v>0.1468</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1751</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1751</v>
+        <v>1.3709</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9971</v>
+        <v>0.4532</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0692</v>
+        <v>-0.3794</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0722</v>
+        <v>0.8325</v>
       </c>
       <c r="V3" t="n">
-        <v>3.1592</v>
+        <v>1.2767</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.9426</v>
+        <v>1.2767</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0409</v>
+        <v>3.74</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6291</v>
+        <v>4.1143</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.3743</v>
       </c>
       <c r="G4" t="n">
         <v>2.9432</v>
@@ -766,13 +766,13 @@
         <v>2.1543</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4483</v>
+        <v>-0.7493</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9922</v>
+        <v>-0.507</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4562</v>
+        <v>-0.2423</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6083</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. BARREIRO BUCETA</t>
+          <t>C. VALDES ALVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5426</v>
+        <v>1.6833</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7264</v>
+        <v>3.5221</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1838</v>
+        <v>-1.8388</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9989</v>
+        <v>0.899</v>
       </c>
       <c r="H5" t="n">
-        <v>0.62</v>
+        <v>1.5353</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3789</v>
+        <v>-0.6363</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4082</v>
+        <v>2.574</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0448</v>
+        <v>3.0946</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3634</v>
+        <v>-0.5206</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4093</v>
+        <v>-1.6749</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4249</v>
+        <v>-1.5593</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0156</v>
+        <v>-0.1157</v>
       </c>
       <c r="P5" t="n">
+        <v>1.1751</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-0.9792</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-2.9377</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.9585</v>
+        <v>2.1543</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5283</v>
+        <v>-1.2104</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3723</v>
+        <v>-0.5058</v>
       </c>
       <c r="U5" t="n">
-        <v>0.156</v>
+        <v>-0.7046</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0053</v>
+        <v>0.8196</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8837</v>
+        <v>2.4332</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.889</v>
+        <v>-1.6136</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. VALDES ALVAREZ</t>
+          <t>N. BARREIRO BUCETA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3507</v>
+        <v>0.9686</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4033</v>
+        <v>2.3929</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0527</v>
+        <v>-1.4243</v>
       </c>
       <c r="G6" t="n">
-        <v>0.899</v>
+        <v>2.9989</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5353</v>
+        <v>0.62</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6363</v>
+        <v>2.3789</v>
       </c>
       <c r="J6" t="n">
-        <v>2.574</v>
+        <v>4.4082</v>
       </c>
       <c r="K6" t="n">
-        <v>3.0946</v>
+        <v>2.0448</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5206</v>
+        <v>2.3634</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6749</v>
+        <v>-1.4093</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5593</v>
+        <v>-1.4249</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1157</v>
+        <v>0.0156</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1751</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1543</v>
+        <v>1.9585</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.543</v>
+        <v>-0.0457</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6246</v>
+        <v>0.0388</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9184</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8196</v>
+        <v>-1.0053</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4332</v>
+        <v>0.8837</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.6136</v>
+        <v>-1.889</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. LOPE REBOLLO</t>
+          <t>A. BELLON LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3028</v>
+        <v>-0.2643</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7211</v>
+        <v>0.1467</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4183</v>
+        <v>-0.411</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3053</v>
+        <v>-0.2137</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2998</v>
+        <v>-0.4362</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0056</v>
+        <v>0.2225</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2428</v>
+        <v>0.4602</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6414</v>
+        <v>0.3793</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6014</v>
+        <v>0.0808</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0625</v>
+        <v>-0.6739000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3416</v>
+        <v>-0.8156</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4042</v>
+        <v>0.1416</v>
       </c>
       <c r="P7" t="n">
         <v>0.3917</v>
@@ -1000,28 +1000,28 @@
         <v>0.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6108</v>
+        <v>0.2211</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5217000000000001</v>
+        <v>-0.3135</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0891</v>
+        <v>0.5346</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.6634</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6634</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BELLON LOPEZ</t>
+          <t>S. LOPE REBOLLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4735</v>
+        <v>-0.5191</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0444</v>
+        <v>-1.0711</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5179</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2137</v>
+        <v>-1.3053</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4362</v>
+        <v>-0.2998</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2225</v>
+        <v>-1.0056</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4602</v>
+        <v>-1.2428</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3793</v>
+        <v>-0.6414</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0808</v>
+        <v>-0.6014</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6739000000000001</v>
+        <v>-0.0625</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8156</v>
+        <v>0.3416</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1416</v>
+        <v>-0.4042</v>
       </c>
       <c r="P8" t="n">
         <v>0.3917</v>
@@ -1078,22 +1078,22 @@
         <v>0.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0119</v>
+        <v>0.3945</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4158</v>
+        <v>0.1717</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4277</v>
+        <v>0.2228</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6634</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8873</v>
+        <v>-1.7315</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7584</v>
+        <v>-1.6561</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1288</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0031</v>
@@ -1156,13 +1156,13 @@
         <v>0.5875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4925</v>
+        <v>-0.3367</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1782</v>
+        <v>-0.0759</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3143</v>
+        <v>-0.2608</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9378</v>
+        <v>-1.8411</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9392</v>
+        <v>-1.9227</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0014</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9004</v>
@@ -1234,13 +1234,13 @@
         <v>1.5668</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7123</v>
+        <v>-0.6156</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.09</v>
+        <v>-0.0735</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6223</v>
+        <v>-0.5421</v>
       </c>
       <c r="V10" t="n">
         <v>0.06660000000000001</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.452</v>
+        <v>-2.081</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4234</v>
+        <v>-1.1593</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0286</v>
+        <v>-0.9217</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1878</v>
@@ -1312,13 +1312,13 @@
         <v>0.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4392</v>
+        <v>-0.0682</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1606</v>
+        <v>0.1035</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2787</v>
+        <v>-0.1717</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2166</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.999</v>
+        <v>-2.9059</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4229</v>
+        <v>-2.1159</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5760999999999999</v>
+        <v>-0.79</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1111</v>
@@ -1390,13 +1390,13 @@
         <v>1.5668</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3047</v>
+        <v>-1.2116</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7722</v>
+        <v>-0.4652</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5325</v>
+        <v>-0.7463</v>
       </c>
       <c r="V12" t="n">
         <v>-1.15</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5642</v>
+        <v>6.4552</v>
       </c>
       <c r="E13" t="n">
-        <v>5.590999999999999</v>
+        <v>6.4819</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.02680000000000005</v>
+        <v>-0.02679999999999971</v>
       </c>
       <c r="G13" t="n">
         <v>4.379999999999999</v>
@@ -1462,22 +1462,22 @@
         <v>4.8963</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.8131</v>
+        <v>-8.813099999999999</v>
       </c>
       <c r="R13" t="n">
         <v>13.7093</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.3903</v>
+        <v>-3.4994</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.5405</v>
+        <v>-2.6497</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8498999999999999</v>
+        <v>-0.8496999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6785000000000008</v>
+        <v>0.6784999999999999</v>
       </c>
       <c r="W13" t="n">
         <v>4.2006</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
+          <t>Á. SONEIRA BOO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3173</v>
+        <v>2.5371</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0714</v>
+        <v>2.261</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.754</v>
+        <v>0.2761</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.3538</v>
+        <v>1.9484</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4699</v>
+        <v>-0.4416</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1161</v>
+        <v>2.3901</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3398</v>
+        <v>2.2641</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1581</v>
+        <v>-0.2416</v>
       </c>
       <c r="L14" t="n">
-        <v>1.1817</v>
+        <v>2.5057</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.6936</v>
+        <v>-0.3157</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.628</v>
+        <v>-0.2</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0656</v>
+        <v>-0.1157</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3709</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1958</v>
+        <v>-1.1751</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5668</v>
+        <v>0.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1424</v>
+        <v>0.4884</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5058</v>
+        <v>-0.3199</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6482</v>
+        <v>0.8084</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1578</v>
+        <v>0.8837</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4332</v>
+        <v>1.492</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2754</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Á. SONEIRA BOO</t>
+          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1563</v>
+        <v>2.4418</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7493</v>
+        <v>3.276</v>
       </c>
       <c r="F15" t="n">
-        <v>0.407</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9484</v>
+        <v>-1.3538</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4416</v>
+        <v>-1.4699</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3901</v>
+        <v>0.1161</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2641</v>
+        <v>1.3398</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2416</v>
+        <v>0.1581</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5057</v>
+        <v>1.1817</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3157</v>
+        <v>-2.6936</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2</v>
+        <v>-1.628</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1157</v>
+        <v>-1.0656</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7834</v>
+        <v>1.3709</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1751</v>
+        <v>-0.1958</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3917</v>
+        <v>1.5668</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1076</v>
+        <v>0.2669</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8316</v>
+        <v>-0.3011</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9393</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8837</v>
+        <v>2.1578</v>
       </c>
       <c r="W15" t="n">
-        <v>1.492</v>
+        <v>2.4332</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6083</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. MASEDA SOILAN</t>
+          <t>R. DÍAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1352</v>
+        <v>1.0775</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7719</v>
+        <v>3.5462</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3633</v>
+        <v>-2.4687</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.407</v>
+        <v>3.3004</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5887</v>
+        <v>4.8469</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8183</v>
+        <v>-1.5465</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6825</v>
+        <v>5.9305</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2435</v>
+        <v>6.6791</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.7486</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0895</v>
+        <v>-2.6301</v>
       </c>
       <c r="N16" t="n">
         <v>-1.8322</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2573</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7834</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.1543</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3709</v>
+        <v>1.5668</v>
       </c>
       <c r="S16" t="n">
-        <v>4.1654</v>
+        <v>0.6377</v>
       </c>
       <c r="T16" t="n">
-        <v>3.0836</v>
+        <v>0.2182</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0818</v>
+        <v>0.4195</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1602</v>
+        <v>-2.273</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1602</v>
+        <v>-0.4481</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ TAPIA</t>
+          <t>M. CAMBON DOMINGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3731</v>
+        <v>0.244</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7865</v>
+        <v>-0.0508</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4134</v>
+        <v>0.2949</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4218</v>
+        <v>1.2174</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1389</v>
+        <v>1.6772</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7171</v>
+        <v>-0.4598</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3499</v>
+        <v>1.6028</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9513</v>
+        <v>1.674</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6014</v>
+        <v>-0.0712</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9281</v>
+        <v>-0.3855</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8124</v>
+        <v>0.0031</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1157</v>
+        <v>-0.3886</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5875</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R17" t="n">
         <v>0.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2048</v>
+        <v>-0.0149</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4734</v>
+        <v>-0.3035</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.2886</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6659</v>
+        <v>0.6083</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.0576</v>
+        <v>0.6083</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>S. RODRÍGUEZ TAPIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3376</v>
+        <v>0.1713</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3182</v>
+        <v>0.5818</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.6558</v>
+        <v>-0.4106</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3004</v>
+        <v>0.4218</v>
       </c>
       <c r="H18" t="n">
-        <v>4.8469</v>
+        <v>1.1389</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5465</v>
+        <v>-0.7171</v>
       </c>
       <c r="J18" t="n">
-        <v>5.9305</v>
+        <v>1.3499</v>
       </c>
       <c r="K18" t="n">
-        <v>6.6791</v>
+        <v>1.9513</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7486</v>
+        <v>-0.6014</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6301</v>
+        <v>-0.9281</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.8322</v>
+        <v>-0.8124</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.1157</v>
       </c>
       <c r="P18" t="n">
         <v>-0.5875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1543</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5668</v>
+        <v>0.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7775</v>
+        <v>1.0029</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0098</v>
+        <v>0.2688</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2324</v>
+        <v>0.7341</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.273</v>
+        <v>-0.6659</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.4481</v>
+        <v>-0.0576</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.8249</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CAMBON DOMINGUEZ</t>
+          <t>D. MASEDA SOILAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4354</v>
+        <v>-0.0276</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4602</v>
+        <v>-0.0701</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0248</v>
+        <v>0.0425</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2174</v>
+        <v>-1.407</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6772</v>
+        <v>-0.5887</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4598</v>
+        <v>-0.8183</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6028</v>
+        <v>0.6825</v>
       </c>
       <c r="K19" t="n">
-        <v>1.674</v>
+        <v>1.2435</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0712</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3855</v>
+        <v>-2.0895</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0031</v>
+        <v>-1.8322</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3886</v>
+        <v>-0.2573</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5668</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9585</v>
+        <v>-2.1543</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3917</v>
+        <v>1.3709</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6943</v>
+        <v>2.0026</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7128</v>
+        <v>1.2415</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0185</v>
+        <v>0.7611</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6083</v>
+        <v>0.1602</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6083</v>
+        <v>0.1602</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5534</v>
+        <v>-0.6438</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7996</v>
+        <v>-1.1066</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2462</v>
+        <v>0.4628</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0933</v>
@@ -2014,13 +2014,13 @@
         <v>0.1958</v>
       </c>
       <c r="S20" t="n">
-        <v>0.344</v>
+        <v>0.2536</v>
       </c>
       <c r="T20" t="n">
-        <v>0.504</v>
+        <v>0.197</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.16</v>
+        <v>0.0566</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5481</v>
+        <v>-1.4946</v>
       </c>
       <c r="E21" t="n">
         <v>-0.84</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7081</v>
+        <v>-0.6546</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4055</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1426</v>
+        <v>-0.0891</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1782</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0356</v>
+        <v>0.0891</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2009</v>
+        <v>-2.0718</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2466</v>
+        <v>-0.1442</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9543</v>
+        <v>-1.9276</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0204</v>
@@ -2170,13 +2170,13 @@
         <v>0.1958</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4927</v>
+        <v>-0.3636</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2376</v>
+        <v>-0.1353</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2551</v>
+        <v>-0.2283</v>
       </c>
       <c r="V22" t="n">
         <v>-0.8837</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6337</v>
+        <v>-2.4733</v>
       </c>
       <c r="E23" t="n">
         <v>-2.3606</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2731</v>
+        <v>-0.1127</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6955</v>
@@ -2248,13 +2248,13 @@
         <v>1.1751</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1548</v>
+        <v>0.0056</v>
       </c>
       <c r="T23" t="n">
         <v>0.1476</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3024</v>
+        <v>-0.142</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8372</v>
+        <v>-4.6427</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.9636</v>
+        <v>-5.0659</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1264</v>
+        <v>0.4232</v>
       </c>
       <c r="G24" t="n">
         <v>-3.2925</v>
@@ -2326,13 +2326,13 @@
         <v>1.5668</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.8825</v>
       </c>
       <c r="T24" t="n">
-        <v>0.117</v>
+        <v>0.0147</v>
       </c>
       <c r="U24" t="n">
-        <v>0.571</v>
+        <v>0.8678</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6659</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.564400000000001</v>
+        <v>-4.882099999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>0.02670000000000083</v>
+        <v>0.02679999999999971</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.591</v>
+        <v>-4.908900000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-4.380000000000001</v>
@@ -2404,13 +2404,13 @@
         <v>8.8131</v>
       </c>
       <c r="S25" t="n">
-        <v>4.3903</v>
+        <v>5.0726</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8497999999999999</v>
+        <v>0.8498</v>
       </c>
       <c r="U25" t="n">
-        <v>3.5407</v>
+        <v>4.2229</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6785000000000003</v>
